--- a/course_registration_form_templates/008_curriculum_co_creation_group_registration_form--course_registration_form_templates.xlsx
+++ b/course_registration_form_templates/008_curriculum_co_creation_group_registration_form--course_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input</t>
+          <t>group_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Group Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>group_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Group Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>group_leader_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Group Leader's Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>group_role</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Group Role</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>course_title</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Course Title</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>group_purpose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>User Input 2</t>
+          <t>Group Purpose</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,35 +704,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>group_size</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Group Size</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>group_meeting_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Group Meeting Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>role_2</t>
+          <t>group_meeting_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Group Meeting Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,39 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>department_2</t>
+          <t>group_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Group Location</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>course_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Course</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,11 +799,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -850,68 +827,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>group_role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>group_role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>role_2_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>role_2_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
